--- a/outputs/product-catalog-rebuild/TECHM8_Tablet_Cases_Missing_Costs_Remaining.xlsx
+++ b/outputs/product-catalog-rebuild/TECHM8_Tablet_Cases_Missing_Costs_Remaining.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing Costs" sheetId="1" r:id="Rfcf0f0054eff4617"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing Costs" sheetId="1" r:id="Rab3155ecc09a4017"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -375,7 +375,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="11" t="str">
-        <x:v>No missing costs. All 287 imported product variants have a confirmed cost.</x:v>
+        <x:v>No missing costs. All 283 imported product variants have a confirmed cost.</x:v>
       </x:c>
       <x:c r="B4" s="11"/>
       <x:c r="C4" s="11"/>
